--- a/tests/fixtures/20_sales_report/pattern.xlsx
+++ b/tests/fixtures/20_sales_report/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>config:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>currency.sign</t>
+          <t>h_prod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>€</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -458,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>col_product</t>
+          <t>h_cust</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -468,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Produkt</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -480,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>col_customer</t>
+          <t>h_q1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -490,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kunde</t>
+          <t>Q1</t>
         </is>
       </c>
     </row>
@@ -502,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>col_q1</t>
+          <t>h_q2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -512,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Qrtl 1</t>
+          <t>Q2</t>
         </is>
       </c>
     </row>
@@ -524,7 +529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>col_q2</t>
+          <t>h_q3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -534,7 +539,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Qrtl 2</t>
+          <t>Q3</t>
         </is>
       </c>
     </row>
@@ -546,7 +551,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>col_q3</t>
+          <t>h_q4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -556,19 +561,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Qrtl 3</t>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>col_q4</t>
+          <t>sale.product</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -578,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Qrtl 4</t>
+          <t>.+</t>
         </is>
       </c>
     </row>
@@ -590,7 +595,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>line.product</t>
+          <t>sale.customer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -600,7 +605,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>.+</t>
         </is>
       </c>
     </row>
@@ -612,12 +617,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>line.customer</t>
+          <t>sale.q1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -634,7 +639,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>line.q1</t>
+          <t>sale.q2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -644,7 +649,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -656,7 +661,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>line.q2</t>
+          <t>sale.q3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,7 +671,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -678,7 +683,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>line.q3</t>
+          <t>sale.q4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -688,122 +693,100 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>line.q4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>table:*</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>table:*</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_prod</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>h_cust</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>h_q1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>h_q2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>h_q3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>h_q4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>HEADER:1</t>
+          <t>DATA:*</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>col_product</t>
+          <t>sale.product</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>col_customer</t>
+          <t>sale.customer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>col_q1</t>
+          <t>sale.q1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>col_q2</t>
+          <t>sale.q2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>col_q3</t>
+          <t>sale.q3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>col_q4</t>
+          <t>sale.q4</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DATA:*</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>line.product</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>line.customer</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>line.q1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>line.q2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>line.q3</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>line.q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/20_sales_report/pattern.xlsx
+++ b/tests/fixtures/20_sales_report/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,22 +436,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>config:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>h_prod</t>
+          <t>currency.sign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Product</t>
+          <t>€</t>
         </is>
       </c>
     </row>
@@ -463,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>h_cust</t>
+          <t>col_product</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +468,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Produkt</t>
         </is>
       </c>
     </row>
@@ -485,7 +480,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>h_q1</t>
+          <t>col_customer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +490,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Kunde</t>
         </is>
       </c>
     </row>
@@ -507,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>h_q2</t>
+          <t>col_q1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +512,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Qrtl 1</t>
         </is>
       </c>
     </row>
@@ -529,7 +524,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>h_q3</t>
+          <t>col_q2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Qrtl 2</t>
         </is>
       </c>
     </row>
@@ -551,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>h_q4</t>
+          <t>col_q3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,19 +556,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Qrtl 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sale.product</t>
+          <t>col_q4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,7 +578,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Qrtl 4</t>
         </is>
       </c>
     </row>
@@ -595,7 +590,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sale.customer</t>
+          <t>line.product</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -605,7 +600,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -617,12 +612,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sale.q1</t>
+          <t>line.customer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -639,7 +634,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sale.q2</t>
+          <t>line.q1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -649,7 +644,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+(\.\d{1,2})?</t>
         </is>
       </c>
     </row>
@@ -661,7 +656,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sale.q3</t>
+          <t>line.q2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -671,7 +666,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+(\.\d{1,2})?</t>
         </is>
       </c>
     </row>
@@ -683,7 +678,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sale.q4</t>
+          <t>line.q3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -693,100 +688,122 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+(\.\d{1,2})?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>line.q4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>START:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>h_prod</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>h_cust</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>h_q1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>h_q2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>h_q3</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>h_q4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>col_product</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>col_customer</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>col_q1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>col_q2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>col_q3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>col_q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>sale.product</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>sale.customer</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>sale.q1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>sale.q2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>sale.q3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>sale.q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>line.product</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>line.customer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>line.q1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>line.q2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>line.q3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>line.q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/20_sales_report/pattern.xlsx
+++ b/tests/fixtures/20_sales_report/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>col_customer</t>
+          <t>col_q1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kunde</t>
+          <t>Summe aus Qrtl 1</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>col_q1</t>
+          <t>col_q2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Qrtl 1</t>
+          <t>Summe aus Qrtl 2</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>col_q2</t>
+          <t>col_q3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Qrtl 2</t>
+          <t>Summe aus Qrtl 3</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>col_q3</t>
+          <t>col_q4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -556,19 +556,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Qrtl 3</t>
+          <t>Summe aus Qrtl 4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>col_q4</t>
+          <t>line.product</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Qrtl 4</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>line.product</t>
+          <t>line.q1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>line.customer</t>
+          <t>line.q2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>line.q1</t>
+          <t>line.q3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>line.q2</t>
+          <t>line.q4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,144 +666,90 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>line.q3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>col_product</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>col_q1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>col_q2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>col_q3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>col_q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DATA:*</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>line.product</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>line.q1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>line.q2</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>line.q3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>line.q4</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>START:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>col_product</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>col_customer</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>col_q1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>col_q2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>col_q3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>col_q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DATA:*</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>line.product</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>line.customer</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>line.q1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>line.q2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>line.q3</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>line.q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/20_sales_report/pattern.xlsx
+++ b/tests/fixtures/20_sales_report/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,22 +436,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>config:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>h_prod</t>
+          <t>currency.sign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Product</t>
+          <t>€</t>
         </is>
       </c>
     </row>
@@ -463,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>h_cust</t>
+          <t>col_product</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +468,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Produkt</t>
         </is>
       </c>
     </row>
@@ -485,7 +480,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>h_q1</t>
+          <t>col_q1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +490,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Summe aus Qrtl 1</t>
         </is>
       </c>
     </row>
@@ -507,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>h_q2</t>
+          <t>col_q2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +512,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Summe aus Qrtl 2</t>
         </is>
       </c>
     </row>
@@ -529,7 +524,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>h_q3</t>
+          <t>col_q3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Summe aus Qrtl 3</t>
         </is>
       </c>
     </row>
@@ -551,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>h_q4</t>
+          <t>col_q4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,7 +556,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Summe aus Qrtl 4</t>
         </is>
       </c>
     </row>
@@ -573,7 +568,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sale.product</t>
+          <t>line.product</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,7 +578,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -595,17 +590,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sale.customer</t>
+          <t>line.q1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -617,7 +612,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sale.q1</t>
+          <t>line.q2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,7 +634,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sale.q2</t>
+          <t>line.q3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,7 +656,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sale.q3</t>
+          <t>line.q4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -678,115 +673,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>sale.q4</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>table:*</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>table:*</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>col_product</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>col_q1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>col_q2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>col_q3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>col_q4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEADER:1</t>
+          <t>DATA:*</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_prod</t>
+          <t>line.product</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>h_cust</t>
+          <t>line.q1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>h_q1</t>
+          <t>line.q2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>h_q2</t>
+          <t>line.q3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>h_q3</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>h_q4</t>
+          <t>line.q4</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DATA:*</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>sale.product</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>sale.customer</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>sale.q1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>sale.q2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>sale.q3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>sale.q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
